--- a/reconcile/storage/output/ongoing/ongoing_battery_q.xlsx
+++ b/reconcile/storage/output/ongoing/ongoing_battery_q.xlsx
@@ -451,7 +451,7 @@
         <v>44286</v>
       </c>
       <c r="B2" t="n">
-        <v>975632004.7927805</v>
+        <v>975632004.4959705</v>
       </c>
     </row>
     <row r="3">
@@ -459,7 +459,7 @@
         <v>44377</v>
       </c>
       <c r="B3" t="n">
-        <v>1187824424.748234</v>
+        <v>1203405117.125172</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         <v>44469</v>
       </c>
       <c r="B4" t="n">
-        <v>1180193591.414901</v>
+        <v>1226935668.625172</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         <v>44561</v>
       </c>
       <c r="B5" t="n">
-        <v>1179439701.548401</v>
+        <v>1229672233.833505</v>
       </c>
     </row>
     <row r="6">
@@ -483,7 +483,7 @@
         <v>44651</v>
       </c>
       <c r="B6" t="n">
-        <v>829549477.1894264</v>
+        <v>879782009.4745311</v>
       </c>
     </row>
     <row r="7">
@@ -491,7 +491,7 @@
         <v>44742</v>
       </c>
       <c r="B7" t="n">
-        <v>1108494990.009939</v>
+        <v>1158727522.295044</v>
       </c>
     </row>
     <row r="8">
@@ -499,7 +499,7 @@
         <v>44834</v>
       </c>
       <c r="B8" t="n">
-        <v>1232342930.291425</v>
+        <v>1282575462.589161</v>
       </c>
     </row>
     <row r="9">
@@ -507,7 +507,7 @@
         <v>44926</v>
       </c>
       <c r="B9" t="n">
-        <v>1122769581.799137</v>
+        <v>1226873116.30141</v>
       </c>
     </row>
     <row r="10">
@@ -515,7 +515,7 @@
         <v>45016</v>
       </c>
       <c r="B10" t="n">
-        <v>1358795383.938174</v>
+        <v>1489834419.530083</v>
       </c>
     </row>
     <row r="11">
@@ -523,7 +523,7 @@
         <v>45107</v>
       </c>
       <c r="B11" t="n">
-        <v>1714040042.057832</v>
+        <v>1829498385.233075</v>
       </c>
     </row>
     <row r="12">
@@ -531,7 +531,7 @@
         <v>45199</v>
       </c>
       <c r="B12" t="n">
-        <v>1852077295.360086</v>
+        <v>1936374253.701995</v>
       </c>
     </row>
     <row r="13">
@@ -539,7 +539,7 @@
         <v>45291</v>
       </c>
       <c r="B13" t="n">
-        <v>1954662371.472455</v>
+        <v>2035468874.798486</v>
       </c>
     </row>
     <row r="14">
@@ -547,7 +547,7 @@
         <v>45382</v>
       </c>
       <c r="B14" t="n">
-        <v>2411221911.916485</v>
+        <v>2492028415.263398</v>
       </c>
     </row>
     <row r="15">
@@ -555,7 +555,7 @@
         <v>45473</v>
       </c>
       <c r="B15" t="n">
-        <v>2632791155.822711</v>
+        <v>2713597659.180065</v>
       </c>
     </row>
     <row r="16">
@@ -563,7 +563,7 @@
         <v>45565</v>
       </c>
       <c r="B16" t="n">
-        <v>2615085294.978399</v>
+        <v>2547903149.025303</v>
       </c>
     </row>
     <row r="17">
@@ -571,7 +571,7 @@
         <v>45657</v>
       </c>
       <c r="B17" t="n">
-        <v>2514873558.600366</v>
+        <v>2373697088.029444</v>
       </c>
     </row>
     <row r="18">
@@ -579,7 +579,7 @@
         <v>45747</v>
       </c>
       <c r="B18" t="n">
-        <v>2806865665.150026</v>
+        <v>2630517715.507705</v>
       </c>
     </row>
     <row r="19">
@@ -587,7 +587,7 @@
         <v>45838</v>
       </c>
       <c r="B19" t="n">
-        <v>3031844218.579053</v>
+        <v>2855496268.936732</v>
       </c>
     </row>
     <row r="20">
@@ -595,7 +595,7 @@
         <v>45930</v>
       </c>
       <c r="B20" t="n">
-        <v>3001336174.813221</v>
+        <v>2872047048.700312</v>
       </c>
     </row>
     <row r="21">
@@ -603,7 +603,7 @@
         <v>46022</v>
       </c>
       <c r="B21" t="n">
-        <v>2672556095.613041</v>
+        <v>2637384616.5</v>
       </c>
     </row>
   </sheetData>
